--- a/DataAnalysis/AdditionalModels/Discriminators/LF/0.2/CLSDIV/res_scrimin=0.csv.xlsx
+++ b/DataAnalysis/AdditionalModels/Discriminators/LF/0.2/CLSDIV/res_scrimin=0.csv.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\Discriminators\CI\0.3\CLSDIV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\AdditionalModels\Discriminators\LF\0.2\CLSDIV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26C381B-A411-48BB-AAA8-319D4561F0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2530743-DEA9-4069-B45E-B12321AA0E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0F214021-6FB1-40D5-9709-F0BEE25B15FC}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="37">
   <si>
     <t>Procedo per riga (prima riga, poi seconda riga, …)</t>
   </si>
@@ -129,6 +129,21 @@
   </si>
   <si>
     <t>Acc</t>
+  </si>
+  <si>
+    <t>Matrix</t>
+  </si>
+  <si>
+    <t>Class 0</t>
+  </si>
+  <si>
+    <t>Class 1</t>
+  </si>
+  <si>
+    <t>Class 2</t>
+  </si>
+  <si>
+    <t>CM</t>
   </si>
 </sst>
 </file>
@@ -997,7 +1012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDEE7005-D29F-4A3A-8B33-A4338B8F6744}">
-  <dimension ref="A1:AL44"/>
+  <dimension ref="A1:AL52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" customWidth="1"/>
@@ -1005,10 +1020,18 @@
   <sheetData>
     <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1107,15 +1130,31 @@
       </c>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1">
+        <v>125</v>
+      </c>
+      <c r="D2" s="1">
+        <v>72</v>
+      </c>
+      <c r="E2" s="1">
+        <v>3</v>
+      </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="G2" s="1">
+        <v>125</v>
+      </c>
+      <c r="H2" s="1">
+        <v>72</v>
+      </c>
+      <c r="I2" s="1">
+        <v>3</v>
+      </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1124,19 +1163,19 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1">
         <f>G2+K2+O2</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="Q2" s="1">
         <f>G2+J2+M2</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="R2" s="1">
         <f>H2+K2+N2</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="S2" s="1">
         <f>I2+L2+O2</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T2" s="1">
         <v>200</v>
@@ -1147,21 +1186,21 @@
       <c r="V2" s="1">
         <v>200</v>
       </c>
-      <c r="W2" s="1" t="e">
+      <c r="W2" s="1">
         <f>G2/Q2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X2" s="1" t="e">
+        <v>1</v>
+      </c>
+      <c r="X2" s="1">
         <f>K2/R2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y2" s="1" t="e">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="1">
         <f>O2/S2</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="1">
         <f>G2/T2</f>
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="AA2" s="1">
         <f>K2/U2</f>
@@ -1177,23 +1216,23 @@
       </c>
       <c r="AD2" s="1">
         <f>P2/AC2</f>
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="AF2">
+        <f t="shared" ref="AF2:AK2" si="0">AVERAGE(W2:W10)</f>
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AF2" t="e">
-        <f t="shared" ref="AF2:AK2" si="0">AVERAGE(W2:W10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG2" t="e">
+      <c r="AH2">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="AI2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="AJ2">
         <f t="shared" si="0"/>
@@ -1205,19 +1244,35 @@
       </c>
       <c r="AL2">
         <f>AVERAGE(AD2:AD10)</f>
-        <v>0</v>
+        <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="A3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="1">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1">
+        <v>184</v>
+      </c>
+      <c r="E3" s="1">
+        <v>3</v>
+      </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+      <c r="G3" s="1">
+        <v>140</v>
+      </c>
+      <c r="H3" s="1">
+        <v>59</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1</v>
+      </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1241,15 +1296,31 @@
       <c r="AD3" s="1"/>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="1">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1">
+        <v>180</v>
+      </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+      <c r="G4" s="1">
+        <v>119</v>
+      </c>
+      <c r="H4" s="1">
+        <v>75</v>
+      </c>
+      <c r="I4" s="1">
+        <v>6</v>
+      </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1279,9 +1350,15 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+      <c r="G5" s="1">
+        <v>110</v>
+      </c>
+      <c r="H5" s="1">
+        <v>83</v>
+      </c>
+      <c r="I5" s="1">
+        <v>7</v>
+      </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1306,14 +1383,28 @@
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+      <c r="G6" s="1">
+        <v>113</v>
+      </c>
+      <c r="H6" s="1">
+        <v>82</v>
+      </c>
+      <c r="I6" s="1">
+        <v>5</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1337,15 +1428,31 @@
       <c r="AD6" s="1"/>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="1">
+        <v>140</v>
+      </c>
+      <c r="D7" s="1">
+        <v>59</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="G7" s="1">
+        <v>107</v>
+      </c>
+      <c r="H7" s="1">
+        <v>83</v>
+      </c>
+      <c r="I7" s="1">
+        <v>10</v>
+      </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -1369,15 +1476,31 @@
       <c r="AD7" s="1"/>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="1">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1">
+        <v>191</v>
+      </c>
+      <c r="E8" s="1">
+        <v>5</v>
+      </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+      <c r="G8" s="1">
+        <v>85</v>
+      </c>
+      <c r="H8" s="1">
+        <v>108</v>
+      </c>
+      <c r="I8" s="1">
+        <v>7</v>
+      </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1401,15 +1524,31 @@
       <c r="AD8" s="1"/>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="1">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1">
+        <v>11</v>
+      </c>
+      <c r="E9" s="1">
+        <v>183</v>
+      </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="G9" s="1">
+        <v>117</v>
+      </c>
+      <c r="H9" s="1">
+        <v>82</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -1439,9 +1578,15 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+      <c r="G10" s="1">
+        <v>113</v>
+      </c>
+      <c r="H10" s="1">
+        <v>83</v>
+      </c>
+      <c r="I10" s="1">
+        <v>4</v>
+      </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -1466,14 +1611,28 @@
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+      <c r="G11" s="1">
+        <v>101</v>
+      </c>
+      <c r="H11">
+        <v>92</v>
+      </c>
+      <c r="I11">
+        <v>7</v>
+      </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -1497,15 +1656,31 @@
       <c r="AD11" s="1"/>
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="1">
+        <v>119</v>
+      </c>
+      <c r="D12" s="1">
+        <v>75</v>
+      </c>
+      <c r="E12" s="1">
+        <v>6</v>
+      </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="G12" s="1">
+        <v>126</v>
+      </c>
+      <c r="H12">
+        <v>72</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -1529,11 +1704,21 @@
       <c r="AD12" s="1"/>
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
+      <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+      <c r="D13" s="1">
+        <v>195</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -1561,11 +1746,21 @@
       <c r="AD13" s="1"/>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="1">
+        <v>4</v>
+      </c>
+      <c r="D14" s="1">
+        <v>24</v>
+      </c>
+      <c r="E14" s="1">
+        <v>172</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -1594,10 +1789,18 @@
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
+      <c r="B15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1625,11 +1828,21 @@
       <c r="AD15" s="1"/>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
+      <c r="A16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="1">
+        <v>110</v>
+      </c>
+      <c r="D16" s="1">
+        <v>83</v>
+      </c>
+      <c r="E16" s="1">
+        <v>7</v>
+      </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1657,11 +1870,21 @@
       <c r="AD16" s="1"/>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
+      <c r="A17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="1">
+        <v>6</v>
+      </c>
+      <c r="D17" s="1">
+        <v>193</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -1689,11 +1912,21 @@
       <c r="AD17" s="1"/>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+      <c r="A18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="1">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1">
+        <v>7</v>
+      </c>
+      <c r="E18" s="1">
+        <v>190</v>
+      </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -1754,10 +1987,18 @@
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
+      <c r="B20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -1785,11 +2026,21 @@
       <c r="AD20" s="1"/>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
+      <c r="A21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="1">
+        <v>113</v>
+      </c>
+      <c r="D21" s="1">
+        <v>82</v>
+      </c>
+      <c r="E21" s="1">
+        <v>5</v>
+      </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -1817,11 +2068,21 @@
       <c r="AD21" s="1"/>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
+      <c r="A22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="1">
+        <v>6</v>
+      </c>
+      <c r="D22" s="1">
+        <v>193</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -1849,11 +2110,21 @@
       <c r="AD22" s="1"/>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
+      <c r="A23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="1">
+        <v>4</v>
+      </c>
+      <c r="D23" s="1">
+        <v>15</v>
+      </c>
+      <c r="E23" s="1">
+        <v>181</v>
+      </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -1914,10 +2185,18 @@
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
+      <c r="B25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
@@ -1945,11 +2224,21 @@
       <c r="AD25" s="1"/>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="1">
+        <v>107</v>
+      </c>
+      <c r="D26" s="1">
+        <v>83</v>
+      </c>
+      <c r="E26" s="1">
+        <v>10</v>
+      </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -1977,11 +2266,21 @@
       <c r="AD26" s="1"/>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="1">
+        <v>7</v>
+      </c>
+      <c r="D27" s="1">
+        <v>190</v>
+      </c>
+      <c r="E27" s="1">
+        <v>3</v>
+      </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -2009,11 +2308,21 @@
       <c r="AD27" s="1"/>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="1">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1">
+        <v>17</v>
+      </c>
+      <c r="E28" s="1">
+        <v>180</v>
+      </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -2042,10 +2351,18 @@
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
+      <c r="B29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -2073,11 +2390,21 @@
       <c r="AD29" s="1"/>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
+      <c r="A30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="1">
+        <v>85</v>
+      </c>
+      <c r="D30" s="1">
+        <v>108</v>
+      </c>
+      <c r="E30" s="1">
+        <v>7</v>
+      </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -2105,11 +2432,21 @@
       <c r="AD30" s="1"/>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
+      <c r="A31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="1">
+        <v>6</v>
+      </c>
+      <c r="D31" s="1">
+        <v>191</v>
+      </c>
+      <c r="E31" s="1">
+        <v>3</v>
+      </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -2137,11 +2474,21 @@
       <c r="AD31" s="1"/>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
+      <c r="A32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="1">
+        <v>4</v>
+      </c>
+      <c r="D32" s="1">
+        <v>16</v>
+      </c>
+      <c r="E32" s="1">
+        <v>180</v>
+      </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -2202,10 +2549,18 @@
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
+      <c r="B34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
@@ -2233,11 +2588,21 @@
       <c r="AD34" s="1"/>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="1">
+        <v>117</v>
+      </c>
+      <c r="D35" s="1">
+        <v>82</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -2265,11 +2630,21 @@
       <c r="AD35" s="1"/>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="1">
+        <v>4</v>
+      </c>
+      <c r="D36" s="1">
+        <v>195</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -2297,11 +2672,21 @@
       <c r="AD36" s="1"/>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1">
+        <v>15</v>
+      </c>
+      <c r="E37" s="1">
+        <v>183</v>
+      </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
@@ -2362,10 +2747,18 @@
     </row>
     <row r="39" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
+      <c r="B39" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
@@ -2393,11 +2786,21 @@
       <c r="AD39" s="1"/>
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
+      <c r="A40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="1">
+        <v>113</v>
+      </c>
+      <c r="D40" s="1">
+        <v>83</v>
+      </c>
+      <c r="E40" s="1">
+        <v>4</v>
+      </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -2425,11 +2828,21 @@
       <c r="AD40" s="1"/>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
+      <c r="A41" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="1">
+        <v>9</v>
+      </c>
+      <c r="D41" s="1">
+        <v>190</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -2457,11 +2870,21 @@
       <c r="AD41" s="1"/>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
+      <c r="A42" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="1">
+        <v>4</v>
+      </c>
+      <c r="D42" s="1">
+        <v>20</v>
+      </c>
+      <c r="E42" s="1">
+        <v>176</v>
+      </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -2522,10 +2945,18 @@
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
+      <c r="B44" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -2552,6 +2983,122 @@
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
     </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45">
+        <v>101</v>
+      </c>
+      <c r="D45">
+        <v>92</v>
+      </c>
+      <c r="E45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46">
+        <v>7</v>
+      </c>
+      <c r="D46">
+        <v>192</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" t="s">
+        <v>36</v>
+      </c>
+      <c r="C47">
+        <v>10</v>
+      </c>
+      <c r="D47">
+        <v>18</v>
+      </c>
+      <c r="E47">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" t="s">
+        <v>33</v>
+      </c>
+      <c r="D49" t="s">
+        <v>34</v>
+      </c>
+      <c r="E49" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" t="s">
+        <v>36</v>
+      </c>
+      <c r="C50">
+        <v>126</v>
+      </c>
+      <c r="D50">
+        <v>72</v>
+      </c>
+      <c r="E50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>34</v>
+      </c>
+      <c r="B51" t="s">
+        <v>36</v>
+      </c>
+      <c r="C51">
+        <v>4</v>
+      </c>
+      <c r="D51">
+        <v>194</v>
+      </c>
+      <c r="E51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52" t="s">
+        <v>36</v>
+      </c>
+      <c r="C52">
+        <v>4</v>
+      </c>
+      <c r="D52">
+        <v>22</v>
+      </c>
+      <c r="E52">
+        <v>174</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DataAnalysis/AdditionalModels/Discriminators/LF/0.2/CLSDIV/res_scrimin=0.csv.xlsx
+++ b/DataAnalysis/AdditionalModels/Discriminators/LF/0.2/CLSDIV/res_scrimin=0.csv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\AdditionalModels\Discriminators\LF\0.2\CLSDIV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2530743-DEA9-4069-B45E-B12321AA0E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700757CA-5B16-4E63-9986-8FFB61C1FAC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0F214021-6FB1-40D5-9709-F0BEE25B15FC}"/>
   </bookViews>
@@ -1155,27 +1155,39 @@
       <c r="I2" s="1">
         <v>3</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
+      <c r="J2" s="1">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1">
+        <v>184</v>
+      </c>
+      <c r="L2" s="1">
+        <v>3</v>
+      </c>
+      <c r="M2" s="1">
+        <v>5</v>
+      </c>
+      <c r="N2" s="1">
+        <v>15</v>
+      </c>
+      <c r="O2" s="1">
+        <v>180</v>
+      </c>
       <c r="P2" s="1">
         <f>G2+K2+O2</f>
-        <v>125</v>
+        <v>489</v>
       </c>
       <c r="Q2" s="1">
         <f>G2+J2+M2</f>
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="R2" s="1">
         <f>H2+K2+N2</f>
-        <v>72</v>
+        <v>271</v>
       </c>
       <c r="S2" s="1">
         <f>I2+L2+O2</f>
-        <v>3</v>
+        <v>186</v>
       </c>
       <c r="T2" s="1">
         <v>200</v>
@@ -1188,15 +1200,15 @@
       </c>
       <c r="W2" s="1">
         <f>G2/Q2</f>
-        <v>1</v>
+        <v>0.87412587412587417</v>
       </c>
       <c r="X2" s="1">
         <f>K2/R2</f>
-        <v>0</v>
+        <v>0.6789667896678967</v>
       </c>
       <c r="Y2" s="1">
         <f>O2/S2</f>
-        <v>0</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="Z2" s="1">
         <f>G2/T2</f>
@@ -1204,11 +1216,11 @@
       </c>
       <c r="AA2" s="1">
         <f>K2/U2</f>
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AB2" s="1">
         <f>O2/V2</f>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AC2" s="1">
         <f>SUM(T2:V2)</f>
@@ -1216,35 +1228,35 @@
       </c>
       <c r="AD2" s="1">
         <f>P2/AC2</f>
-        <v>0.20833333333333334</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="AF2">
         <f t="shared" ref="AF2:AK2" si="0">AVERAGE(W2:W10)</f>
-        <v>1</v>
+        <v>0.91609418689129796</v>
       </c>
       <c r="AG2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.66659143390918563</v>
       </c>
       <c r="AH2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.9628862160534738</v>
       </c>
       <c r="AI2">
         <f t="shared" si="0"/>
-        <v>0.625</v>
+        <v>0.57166666666666666</v>
       </c>
       <c r="AJ2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.95666666666666655</v>
       </c>
       <c r="AK2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.90277777777777801</v>
       </c>
       <c r="AL2">
         <f>AVERAGE(AD2:AD10)</f>
-        <v>0.20833333333333334</v>
+        <v>0.8103703703703703</v>
       </c>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.3">
@@ -1273,27 +1285,81 @@
       <c r="I3" s="1">
         <v>1</v>
       </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
-      <c r="AC3" s="1"/>
-      <c r="AD3" s="1"/>
+      <c r="J3" s="1">
+        <v>4</v>
+      </c>
+      <c r="K3" s="1">
+        <v>191</v>
+      </c>
+      <c r="L3" s="1">
+        <v>5</v>
+      </c>
+      <c r="M3" s="1">
+        <v>6</v>
+      </c>
+      <c r="N3" s="1">
+        <v>11</v>
+      </c>
+      <c r="O3" s="1">
+        <v>183</v>
+      </c>
+      <c r="P3" s="1">
+        <f t="shared" ref="P3:P12" si="1">G3+K3+O3</f>
+        <v>514</v>
+      </c>
+      <c r="Q3" s="1">
+        <f t="shared" ref="Q3:Q12" si="2">G3+J3+M3</f>
+        <v>150</v>
+      </c>
+      <c r="R3" s="1">
+        <f t="shared" ref="R3:R12" si="3">H3+K3+N3</f>
+        <v>261</v>
+      </c>
+      <c r="S3" s="1">
+        <f t="shared" ref="S3:S12" si="4">I3+L3+O3</f>
+        <v>189</v>
+      </c>
+      <c r="T3" s="1">
+        <v>200</v>
+      </c>
+      <c r="U3" s="1">
+        <v>200</v>
+      </c>
+      <c r="V3" s="1">
+        <v>200</v>
+      </c>
+      <c r="W3" s="1">
+        <f t="shared" ref="W3:W12" si="5">G3/Q3</f>
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="X3" s="1">
+        <f t="shared" ref="X3:X12" si="6">K3/R3</f>
+        <v>0.73180076628352486</v>
+      </c>
+      <c r="Y3" s="1">
+        <f t="shared" ref="Y3:Y12" si="7">O3/S3</f>
+        <v>0.96825396825396826</v>
+      </c>
+      <c r="Z3" s="1">
+        <f t="shared" ref="Z3:Z12" si="8">G3/T3</f>
+        <v>0.7</v>
+      </c>
+      <c r="AA3" s="1">
+        <f t="shared" ref="AA3:AA12" si="9">K3/U3</f>
+        <v>0.95499999999999996</v>
+      </c>
+      <c r="AB3" s="1">
+        <f t="shared" ref="AB3:AB12" si="10">O3/V3</f>
+        <v>0.91500000000000004</v>
+      </c>
+      <c r="AC3" s="1">
+        <f t="shared" ref="AC3:AC12" si="11">SUM(T3:V3)</f>
+        <v>600</v>
+      </c>
+      <c r="AD3" s="1">
+        <f t="shared" ref="AD3:AD12" si="12">P3/AC3</f>
+        <v>0.85666666666666669</v>
+      </c>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1321,27 +1387,81 @@
       <c r="I4" s="1">
         <v>6</v>
       </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
+      <c r="J4" s="1">
+        <v>4</v>
+      </c>
+      <c r="K4" s="1">
+        <v>195</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1">
+        <v>4</v>
+      </c>
+      <c r="N4" s="1">
+        <v>24</v>
+      </c>
+      <c r="O4" s="1">
+        <v>172</v>
+      </c>
+      <c r="P4" s="1">
+        <f t="shared" si="1"/>
+        <v>486</v>
+      </c>
+      <c r="Q4" s="1">
+        <f t="shared" si="2"/>
+        <v>127</v>
+      </c>
+      <c r="R4" s="1">
+        <f t="shared" si="3"/>
+        <v>294</v>
+      </c>
+      <c r="S4" s="1">
+        <f t="shared" si="4"/>
+        <v>179</v>
+      </c>
+      <c r="T4" s="1">
+        <v>200</v>
+      </c>
+      <c r="U4" s="1">
+        <v>200</v>
+      </c>
+      <c r="V4" s="1">
+        <v>200</v>
+      </c>
+      <c r="W4" s="1">
+        <f t="shared" si="5"/>
+        <v>0.93700787401574803</v>
+      </c>
+      <c r="X4" s="1">
+        <f t="shared" si="6"/>
+        <v>0.66326530612244894</v>
+      </c>
+      <c r="Y4" s="1">
+        <f t="shared" si="7"/>
+        <v>0.96089385474860334</v>
+      </c>
+      <c r="Z4" s="1">
+        <f t="shared" si="8"/>
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" si="9"/>
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="AB4" s="1">
+        <f t="shared" si="10"/>
+        <v>0.86</v>
+      </c>
+      <c r="AC4" s="1">
+        <f t="shared" si="11"/>
+        <v>600</v>
+      </c>
+      <c r="AD4" s="1">
+        <f t="shared" si="12"/>
+        <v>0.81</v>
+      </c>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
@@ -1359,27 +1479,81 @@
       <c r="I5" s="1">
         <v>7</v>
       </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="1"/>
+      <c r="J5" s="1">
+        <v>6</v>
+      </c>
+      <c r="K5" s="1">
+        <v>193</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1">
+        <v>3</v>
+      </c>
+      <c r="N5" s="1">
+        <v>7</v>
+      </c>
+      <c r="O5" s="1">
+        <v>190</v>
+      </c>
+      <c r="P5" s="1">
+        <f t="shared" si="1"/>
+        <v>493</v>
+      </c>
+      <c r="Q5" s="1">
+        <f t="shared" si="2"/>
+        <v>119</v>
+      </c>
+      <c r="R5" s="1">
+        <f t="shared" si="3"/>
+        <v>283</v>
+      </c>
+      <c r="S5" s="1">
+        <f t="shared" si="4"/>
+        <v>198</v>
+      </c>
+      <c r="T5" s="1">
+        <v>200</v>
+      </c>
+      <c r="U5" s="1">
+        <v>200</v>
+      </c>
+      <c r="V5" s="1">
+        <v>200</v>
+      </c>
+      <c r="W5" s="1">
+        <f t="shared" si="5"/>
+        <v>0.92436974789915971</v>
+      </c>
+      <c r="X5" s="1">
+        <f t="shared" si="6"/>
+        <v>0.6819787985865724</v>
+      </c>
+      <c r="Y5" s="1">
+        <f t="shared" si="7"/>
+        <v>0.95959595959595956</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" si="8"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AA5" s="1">
+        <f t="shared" si="9"/>
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="AB5" s="1">
+        <f t="shared" si="10"/>
+        <v>0.95</v>
+      </c>
+      <c r="AC5" s="1">
+        <f t="shared" si="11"/>
+        <v>600</v>
+      </c>
+      <c r="AD5" s="1">
+        <f t="shared" si="12"/>
+        <v>0.82166666666666666</v>
+      </c>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -1405,27 +1579,81 @@
       <c r="I6" s="1">
         <v>5</v>
       </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="1"/>
-      <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
+      <c r="J6" s="1">
+        <v>6</v>
+      </c>
+      <c r="K6" s="1">
+        <v>193</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>4</v>
+      </c>
+      <c r="N6" s="1">
+        <v>15</v>
+      </c>
+      <c r="O6" s="1">
+        <v>181</v>
+      </c>
+      <c r="P6" s="1">
+        <f t="shared" si="1"/>
+        <v>487</v>
+      </c>
+      <c r="Q6" s="1">
+        <f t="shared" si="2"/>
+        <v>123</v>
+      </c>
+      <c r="R6" s="1">
+        <f t="shared" si="3"/>
+        <v>290</v>
+      </c>
+      <c r="S6" s="1">
+        <f t="shared" si="4"/>
+        <v>187</v>
+      </c>
+      <c r="T6" s="1">
+        <v>200</v>
+      </c>
+      <c r="U6" s="1">
+        <v>200</v>
+      </c>
+      <c r="V6" s="1">
+        <v>200</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" si="5"/>
+        <v>0.91869918699186992</v>
+      </c>
+      <c r="X6" s="1">
+        <f t="shared" si="6"/>
+        <v>0.66551724137931034</v>
+      </c>
+      <c r="Y6" s="1">
+        <f t="shared" si="7"/>
+        <v>0.96791443850267378</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" si="8"/>
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="AA6" s="1">
+        <f t="shared" si="9"/>
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="AB6" s="1">
+        <f t="shared" si="10"/>
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" si="11"/>
+        <v>600</v>
+      </c>
+      <c r="AD6" s="1">
+        <f t="shared" si="12"/>
+        <v>0.81166666666666665</v>
+      </c>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -1453,27 +1681,81 @@
       <c r="I7" s="1">
         <v>10</v>
       </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-      <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="1"/>
-      <c r="AC7" s="1"/>
-      <c r="AD7" s="1"/>
+      <c r="J7" s="1">
+        <v>7</v>
+      </c>
+      <c r="K7" s="1">
+        <v>190</v>
+      </c>
+      <c r="L7" s="1">
+        <v>3</v>
+      </c>
+      <c r="M7" s="1">
+        <v>3</v>
+      </c>
+      <c r="N7" s="1">
+        <v>17</v>
+      </c>
+      <c r="O7" s="1">
+        <v>180</v>
+      </c>
+      <c r="P7" s="1">
+        <f t="shared" si="1"/>
+        <v>477</v>
+      </c>
+      <c r="Q7" s="1">
+        <f t="shared" si="2"/>
+        <v>117</v>
+      </c>
+      <c r="R7" s="1">
+        <f t="shared" si="3"/>
+        <v>290</v>
+      </c>
+      <c r="S7" s="1">
+        <f t="shared" si="4"/>
+        <v>193</v>
+      </c>
+      <c r="T7" s="1">
+        <v>200</v>
+      </c>
+      <c r="U7" s="1">
+        <v>200</v>
+      </c>
+      <c r="V7" s="1">
+        <v>200</v>
+      </c>
+      <c r="W7" s="1">
+        <f t="shared" si="5"/>
+        <v>0.9145299145299145</v>
+      </c>
+      <c r="X7" s="1">
+        <f t="shared" si="6"/>
+        <v>0.65517241379310343</v>
+      </c>
+      <c r="Y7" s="1">
+        <f t="shared" si="7"/>
+        <v>0.93264248704663211</v>
+      </c>
+      <c r="Z7" s="1">
+        <f t="shared" si="8"/>
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="AA7" s="1">
+        <f t="shared" si="9"/>
+        <v>0.95</v>
+      </c>
+      <c r="AB7" s="1">
+        <f t="shared" si="10"/>
+        <v>0.9</v>
+      </c>
+      <c r="AC7" s="1">
+        <f t="shared" si="11"/>
+        <v>600</v>
+      </c>
+      <c r="AD7" s="1">
+        <f t="shared" si="12"/>
+        <v>0.79500000000000004</v>
+      </c>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -1501,27 +1783,81 @@
       <c r="I8" s="1">
         <v>7</v>
       </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-      <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="1"/>
-      <c r="AC8" s="1"/>
-      <c r="AD8" s="1"/>
+      <c r="J8" s="1">
+        <v>6</v>
+      </c>
+      <c r="K8" s="1">
+        <v>191</v>
+      </c>
+      <c r="L8" s="1">
+        <v>3</v>
+      </c>
+      <c r="M8" s="1">
+        <v>4</v>
+      </c>
+      <c r="N8" s="1">
+        <v>16</v>
+      </c>
+      <c r="O8" s="1">
+        <v>180</v>
+      </c>
+      <c r="P8" s="1">
+        <f t="shared" si="1"/>
+        <v>456</v>
+      </c>
+      <c r="Q8" s="1">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="R8" s="1">
+        <f t="shared" si="3"/>
+        <v>315</v>
+      </c>
+      <c r="S8" s="1">
+        <f t="shared" si="4"/>
+        <v>190</v>
+      </c>
+      <c r="T8" s="1">
+        <v>200</v>
+      </c>
+      <c r="U8" s="1">
+        <v>200</v>
+      </c>
+      <c r="V8" s="1">
+        <v>200</v>
+      </c>
+      <c r="W8" s="1">
+        <f t="shared" si="5"/>
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="X8" s="1">
+        <f t="shared" si="6"/>
+        <v>0.6063492063492063</v>
+      </c>
+      <c r="Y8" s="1">
+        <f t="shared" si="7"/>
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="Z8" s="1">
+        <f t="shared" si="8"/>
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="AA8" s="1">
+        <f t="shared" si="9"/>
+        <v>0.95499999999999996</v>
+      </c>
+      <c r="AB8" s="1">
+        <f t="shared" si="10"/>
+        <v>0.9</v>
+      </c>
+      <c r="AC8" s="1">
+        <f t="shared" si="11"/>
+        <v>600</v>
+      </c>
+      <c r="AD8" s="1">
+        <f t="shared" si="12"/>
+        <v>0.76</v>
+      </c>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -1549,27 +1885,81 @@
       <c r="I9" s="1">
         <v>1</v>
       </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
-      <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="1"/>
-      <c r="AC9" s="1"/>
-      <c r="AD9" s="1"/>
+      <c r="J9" s="1">
+        <v>4</v>
+      </c>
+      <c r="K9" s="1">
+        <v>195</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1">
+        <v>2</v>
+      </c>
+      <c r="N9" s="1">
+        <v>15</v>
+      </c>
+      <c r="O9" s="1">
+        <v>183</v>
+      </c>
+      <c r="P9" s="1">
+        <f t="shared" si="1"/>
+        <v>495</v>
+      </c>
+      <c r="Q9" s="1">
+        <f t="shared" si="2"/>
+        <v>123</v>
+      </c>
+      <c r="R9" s="1">
+        <f t="shared" si="3"/>
+        <v>292</v>
+      </c>
+      <c r="S9" s="1">
+        <f t="shared" si="4"/>
+        <v>185</v>
+      </c>
+      <c r="T9" s="1">
+        <v>200</v>
+      </c>
+      <c r="U9" s="1">
+        <v>200</v>
+      </c>
+      <c r="V9" s="1">
+        <v>200</v>
+      </c>
+      <c r="W9" s="1">
+        <f t="shared" si="5"/>
+        <v>0.95121951219512191</v>
+      </c>
+      <c r="X9" s="1">
+        <f t="shared" si="6"/>
+        <v>0.6678082191780822</v>
+      </c>
+      <c r="Y9" s="1">
+        <f t="shared" si="7"/>
+        <v>0.98918918918918919</v>
+      </c>
+      <c r="Z9" s="1">
+        <f t="shared" si="8"/>
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="AA9" s="1">
+        <f t="shared" si="9"/>
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="AB9" s="1">
+        <f t="shared" si="10"/>
+        <v>0.91500000000000004</v>
+      </c>
+      <c r="AC9" s="1">
+        <f t="shared" si="11"/>
+        <v>600</v>
+      </c>
+      <c r="AD9" s="1">
+        <f t="shared" si="12"/>
+        <v>0.82499999999999996</v>
+      </c>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
@@ -1587,27 +1977,81 @@
       <c r="I10" s="1">
         <v>4</v>
       </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
-      <c r="Z10" s="1"/>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="1"/>
-      <c r="AC10" s="1"/>
-      <c r="AD10" s="1"/>
+      <c r="J10" s="1">
+        <v>9</v>
+      </c>
+      <c r="K10" s="1">
+        <v>190</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1">
+        <v>4</v>
+      </c>
+      <c r="N10" s="1">
+        <v>20</v>
+      </c>
+      <c r="O10" s="1">
+        <v>176</v>
+      </c>
+      <c r="P10" s="1">
+        <f t="shared" si="1"/>
+        <v>479</v>
+      </c>
+      <c r="Q10" s="1">
+        <f t="shared" si="2"/>
+        <v>126</v>
+      </c>
+      <c r="R10" s="1">
+        <f t="shared" si="3"/>
+        <v>293</v>
+      </c>
+      <c r="S10" s="1">
+        <f t="shared" si="4"/>
+        <v>181</v>
+      </c>
+      <c r="T10" s="1">
+        <v>200</v>
+      </c>
+      <c r="U10" s="1">
+        <v>200</v>
+      </c>
+      <c r="V10" s="1">
+        <v>200</v>
+      </c>
+      <c r="W10" s="1">
+        <f t="shared" si="5"/>
+        <v>0.89682539682539686</v>
+      </c>
+      <c r="X10" s="1">
+        <f t="shared" si="6"/>
+        <v>0.64846416382252559</v>
+      </c>
+      <c r="Y10" s="1">
+        <f t="shared" si="7"/>
+        <v>0.97237569060773477</v>
+      </c>
+      <c r="Z10" s="1">
+        <f t="shared" si="8"/>
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="AA10" s="1">
+        <f t="shared" si="9"/>
+        <v>0.95</v>
+      </c>
+      <c r="AB10" s="1">
+        <f t="shared" si="10"/>
+        <v>0.88</v>
+      </c>
+      <c r="AC10" s="1">
+        <f t="shared" si="11"/>
+        <v>600</v>
+      </c>
+      <c r="AD10" s="1">
+        <f t="shared" si="12"/>
+        <v>0.79833333333333334</v>
+      </c>
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
@@ -1633,27 +2077,81 @@
       <c r="I11">
         <v>7</v>
       </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
-      <c r="Z11" s="1"/>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="1"/>
-      <c r="AC11" s="1"/>
-      <c r="AD11" s="1"/>
+      <c r="J11">
+        <v>7</v>
+      </c>
+      <c r="K11">
+        <v>192</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
+      </c>
+      <c r="N11">
+        <v>18</v>
+      </c>
+      <c r="O11">
+        <v>172</v>
+      </c>
+      <c r="P11" s="1">
+        <f t="shared" si="1"/>
+        <v>465</v>
+      </c>
+      <c r="Q11" s="1">
+        <f t="shared" si="2"/>
+        <v>118</v>
+      </c>
+      <c r="R11" s="1">
+        <f t="shared" si="3"/>
+        <v>302</v>
+      </c>
+      <c r="S11" s="1">
+        <f t="shared" si="4"/>
+        <v>180</v>
+      </c>
+      <c r="T11" s="1">
+        <v>200</v>
+      </c>
+      <c r="U11" s="1">
+        <v>200</v>
+      </c>
+      <c r="V11" s="1">
+        <v>200</v>
+      </c>
+      <c r="W11" s="1">
+        <f t="shared" si="5"/>
+        <v>0.85593220338983056</v>
+      </c>
+      <c r="X11" s="1">
+        <f t="shared" si="6"/>
+        <v>0.63576158940397354</v>
+      </c>
+      <c r="Y11" s="1">
+        <f t="shared" si="7"/>
+        <v>0.9555555555555556</v>
+      </c>
+      <c r="Z11" s="1">
+        <f t="shared" si="8"/>
+        <v>0.505</v>
+      </c>
+      <c r="AA11" s="1">
+        <f t="shared" si="9"/>
+        <v>0.96</v>
+      </c>
+      <c r="AB11" s="1">
+        <f t="shared" si="10"/>
+        <v>0.86</v>
+      </c>
+      <c r="AC11" s="1">
+        <f t="shared" si="11"/>
+        <v>600</v>
+      </c>
+      <c r="AD11" s="1">
+        <f t="shared" si="12"/>
+        <v>0.77500000000000002</v>
+      </c>
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -1681,27 +2179,81 @@
       <c r="I12">
         <v>2</v>
       </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="1"/>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
-      <c r="Z12" s="1"/>
-      <c r="AA12" s="1"/>
-      <c r="AB12" s="1"/>
-      <c r="AC12" s="1"/>
-      <c r="AD12" s="1"/>
+      <c r="J12">
+        <v>4</v>
+      </c>
+      <c r="K12">
+        <v>194</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12">
+        <v>4</v>
+      </c>
+      <c r="N12">
+        <v>22</v>
+      </c>
+      <c r="O12">
+        <v>174</v>
+      </c>
+      <c r="P12" s="1">
+        <f t="shared" si="1"/>
+        <v>494</v>
+      </c>
+      <c r="Q12" s="1">
+        <f t="shared" si="2"/>
+        <v>134</v>
+      </c>
+      <c r="R12" s="1">
+        <f t="shared" si="3"/>
+        <v>288</v>
+      </c>
+      <c r="S12" s="1">
+        <f t="shared" si="4"/>
+        <v>178</v>
+      </c>
+      <c r="T12" s="1">
+        <v>200</v>
+      </c>
+      <c r="U12" s="1">
+        <v>200</v>
+      </c>
+      <c r="V12" s="1">
+        <v>200</v>
+      </c>
+      <c r="W12" s="1">
+        <f t="shared" si="5"/>
+        <v>0.94029850746268662</v>
+      </c>
+      <c r="X12" s="1">
+        <f t="shared" si="6"/>
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="Y12" s="1">
+        <f t="shared" si="7"/>
+        <v>0.97752808988764039</v>
+      </c>
+      <c r="Z12" s="1">
+        <f t="shared" si="8"/>
+        <v>0.63</v>
+      </c>
+      <c r="AA12" s="1">
+        <f t="shared" si="9"/>
+        <v>0.97</v>
+      </c>
+      <c r="AB12" s="1">
+        <f t="shared" si="10"/>
+        <v>0.87</v>
+      </c>
+      <c r="AC12" s="1">
+        <f t="shared" si="11"/>
+        <v>600</v>
+      </c>
+      <c r="AD12" s="1">
+        <f t="shared" si="12"/>
+        <v>0.82333333333333336</v>
+      </c>
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
